--- a/5/search/FY4_Missile2_results/fine_tuned/all_fine_tuned_solutions.xlsx
+++ b/5/search/FY4_Missile2_results/fine_tuned/all_fine_tuned_solutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L60"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,37 +492,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B2" t="n">
-        <v>98.3</v>
+        <v>102.8</v>
       </c>
       <c r="C2" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>11299.58918545787</v>
+        <v>11227.58516269173</v>
       </c>
       <c r="F2" t="n">
-        <v>1294.212108663876</v>
+        <v>1339.044694913054</v>
       </c>
       <c r="G2" t="n">
         <v>1800</v>
       </c>
       <c r="H2" t="n">
-        <v>11683.67788476282</v>
+        <v>11562.26922547369</v>
       </c>
       <c r="I2" t="n">
-        <v>389.3558377201269</v>
+        <v>367.051599196956</v>
       </c>
       <c r="J2" t="n">
         <v>1310</v>
       </c>
       <c r="K2" t="n">
-        <v>1.199999999999999</v>
+        <v>0.7999999999999972</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -530,37 +530,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>293</v>
+        <v>290.6</v>
       </c>
       <c r="B3" t="n">
-        <v>99.3</v>
+        <v>96.8</v>
       </c>
       <c r="C3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>11302.63688826008</v>
+        <v>11272.4661725246</v>
       </c>
       <c r="F3" t="n">
-        <v>1287.032170806947</v>
+        <v>1275.115495523739</v>
       </c>
       <c r="G3" t="n">
         <v>1800</v>
       </c>
       <c r="H3" t="n">
-        <v>11690.63289884993</v>
+        <v>11613.04888818035</v>
       </c>
       <c r="I3" t="n">
-        <v>372.9708513286735</v>
+        <v>369.0098649284134</v>
       </c>
       <c r="J3" t="n">
         <v>1310</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>1.199999999999999</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -568,10 +568,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>293</v>
+        <v>290.6</v>
       </c>
       <c r="B4" t="n">
-        <v>101.3</v>
+        <v>99.8</v>
       </c>
       <c r="C4" t="n">
         <v>7.4</v>
@@ -580,25 +580,25 @@
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>11292.89986853813</v>
+        <v>11259.84209417984</v>
       </c>
       <c r="F4" t="n">
-        <v>1309.971151754982</v>
+        <v>1308.701311666054</v>
       </c>
       <c r="G4" t="n">
         <v>1800</v>
       </c>
       <c r="H4" t="n">
-        <v>11688.71050169776</v>
+        <v>11610.98005928773</v>
       </c>
       <c r="I4" t="n">
-        <v>377.4997352076595</v>
+        <v>374.5138949985587</v>
       </c>
       <c r="J4" t="n">
         <v>1310</v>
       </c>
       <c r="K4" t="n">
-        <v>3.300000000000001</v>
+        <v>1.900000000000002</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -606,10 +606,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>293</v>
+        <v>290.6</v>
       </c>
       <c r="B5" t="n">
-        <v>102.3</v>
+        <v>100.8</v>
       </c>
       <c r="C5" t="n">
         <v>7.4</v>
@@ -618,25 +618,25 @@
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>11295.79127888895</v>
+        <v>11262.44572237804</v>
       </c>
       <c r="F5" t="n">
-        <v>1303.159415839433</v>
+        <v>1301.774471101585</v>
       </c>
       <c r="G5" t="n">
         <v>1800</v>
       </c>
       <c r="H5" t="n">
-        <v>11695.50922333348</v>
+        <v>11617.10210396998</v>
       </c>
       <c r="I5" t="n">
-        <v>361.482950757587</v>
+        <v>358.2264590767007</v>
       </c>
       <c r="J5" t="n">
         <v>1310</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3999999999999986</v>
+        <v>0.09999999999999787</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -644,37 +644,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>293</v>
+        <v>290.6</v>
       </c>
       <c r="B6" t="n">
-        <v>103.3</v>
+        <v>103.8</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>11282.53767901059</v>
+        <v>11248.34390910998</v>
       </c>
       <c r="F6" t="n">
-        <v>1334.38294046854</v>
+        <v>1339.291737294003</v>
       </c>
       <c r="G6" t="n">
         <v>1800</v>
       </c>
       <c r="H6" t="n">
-        <v>11686.16293474001</v>
+        <v>11613.55554015406</v>
       </c>
       <c r="I6" t="n">
-        <v>383.5014268521693</v>
+        <v>367.6619391969492</v>
       </c>
       <c r="J6" t="n">
         <v>1310</v>
       </c>
       <c r="K6" t="n">
-        <v>3.300000000000001</v>
+        <v>1.699999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -682,37 +682,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>294.6</v>
+        <v>292.2</v>
       </c>
       <c r="B7" t="n">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
       <c r="C7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>11335.54729540942</v>
+        <v>11295.62263160677</v>
       </c>
       <c r="F7" t="n">
-        <v>1267.10114194152</v>
+        <v>1275.59885444466</v>
       </c>
       <c r="G7" t="n">
         <v>1800</v>
       </c>
       <c r="H7" t="n">
-        <v>11744.7513142014</v>
+        <v>11665.15092111523</v>
       </c>
       <c r="I7" t="n">
-        <v>373.3220467482523</v>
+        <v>370.0974225004851</v>
       </c>
       <c r="J7" t="n">
         <v>1310</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5</v>
+        <v>1.900000000000002</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -720,31 +720,31 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>294.6</v>
+        <v>292.2</v>
       </c>
       <c r="B8" t="n">
-        <v>99.3</v>
+        <v>100.8</v>
       </c>
       <c r="C8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>11322.42612483737</v>
+        <v>11281.83899970363</v>
       </c>
       <c r="F8" t="n">
-        <v>1295.760264098684</v>
+        <v>1309.374613378528</v>
       </c>
       <c r="G8" t="n">
         <v>1800</v>
       </c>
       <c r="H8" t="n">
-        <v>11735.79295155195</v>
+        <v>11662.70251281664</v>
       </c>
       <c r="I8" t="n">
-        <v>392.888807814945</v>
+        <v>376.0970638900537</v>
       </c>
       <c r="J8" t="n">
         <v>1310</v>
@@ -758,37 +758,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>294.6</v>
+        <v>292.2</v>
       </c>
       <c r="B9" t="n">
-        <v>100.3</v>
+        <v>101.8</v>
       </c>
       <c r="C9" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>11325.673115017</v>
+        <v>11284.63502152609</v>
       </c>
       <c r="F9" t="n">
-        <v>1288.668222448116</v>
+        <v>1302.523171050935</v>
       </c>
       <c r="G9" t="n">
         <v>1800</v>
       </c>
       <c r="H9" t="n">
-        <v>11743.20274965419</v>
+        <v>11669.27694250729</v>
       </c>
       <c r="I9" t="n">
-        <v>376.704405073907</v>
+        <v>359.9869157143602</v>
       </c>
       <c r="J9" t="n">
         <v>1310</v>
       </c>
       <c r="K9" t="n">
-        <v>3.199999999999999</v>
+        <v>0.3000000000000007</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>294.6</v>
+        <v>292.2</v>
       </c>
       <c r="B10" t="n">
-        <v>101.3</v>
+        <v>103.8</v>
       </c>
       <c r="C10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>11312.05240749424</v>
+        <v>11266.69514096795</v>
       </c>
       <c r="F10" t="n">
-        <v>1318.418427936137</v>
+        <v>1346.483506417713</v>
       </c>
       <c r="G10" t="n">
         <v>1800</v>
       </c>
       <c r="H10" t="n">
-        <v>11733.74485005403</v>
+        <v>11658.89387768551</v>
       </c>
       <c r="I10" t="n">
-        <v>397.3622494714565</v>
+        <v>385.4298393849385</v>
       </c>
       <c r="J10" t="n">
         <v>1310</v>
       </c>
       <c r="K10" t="n">
-        <v>2.199999999999999</v>
+        <v>2.5</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -834,37 +834,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>294.6</v>
+        <v>292.2</v>
       </c>
       <c r="B11" t="n">
-        <v>102.3</v>
+        <v>104.8</v>
       </c>
       <c r="C11" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>11315.13288535697</v>
+        <v>11269.26445831831</v>
       </c>
       <c r="F11" t="n">
-        <v>1311.690080729188</v>
+        <v>1340.187586441005</v>
       </c>
       <c r="G11" t="n">
         <v>1800</v>
       </c>
       <c r="H11" t="n">
-        <v>11740.98813583936</v>
+        <v>11665.24160290407</v>
       </c>
       <c r="I11" t="n">
-        <v>381.5415411740378</v>
+        <v>369.8752135601308</v>
       </c>
       <c r="J11" t="n">
         <v>1310</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>2.200000000000003</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -872,37 +872,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B12" t="n">
-        <v>98.3</v>
+        <v>95.8</v>
       </c>
       <c r="C12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>11355.88020770131</v>
+        <v>11332.47289875881</v>
       </c>
       <c r="F12" t="n">
-        <v>1276.755918540311</v>
+        <v>1246.183028851886</v>
       </c>
       <c r="G12" t="n">
         <v>1800</v>
       </c>
       <c r="H12" t="n">
-        <v>11789.8804609956</v>
+        <v>11719.0692926644</v>
       </c>
       <c r="I12" t="n">
-        <v>394.750941150446</v>
+        <v>369.651667051754</v>
       </c>
       <c r="J12" t="n">
         <v>1310</v>
       </c>
       <c r="K12" t="n">
-        <v>3.200000000000003</v>
+        <v>1.899999999999999</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -910,37 +910,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B13" t="n">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
       <c r="C13" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>11373.24021783308</v>
+        <v>11315.73383986611</v>
       </c>
       <c r="F13" t="n">
-        <v>1241.475719444716</v>
+        <v>1284.135555874297</v>
       </c>
       <c r="G13" t="n">
         <v>1800</v>
       </c>
       <c r="H13" t="n">
-        <v>11798.56046606148</v>
+        <v>11710.40113969875</v>
       </c>
       <c r="I13" t="n">
-        <v>377.1108416026486</v>
+        <v>389.3050007171685</v>
       </c>
       <c r="J13" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6000000000000014</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -948,37 +948,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B14" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="C14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>11359.50055569421</v>
+        <v>11318.96220223693</v>
       </c>
       <c r="F14" t="n">
-        <v>1269.398399908981</v>
+        <v>1276.815878531499</v>
       </c>
       <c r="G14" t="n">
         <v>1800</v>
       </c>
       <c r="H14" t="n">
-        <v>11797.91586751641</v>
+        <v>11717.66495503309</v>
       </c>
       <c r="I14" t="n">
-        <v>378.4208388223733</v>
+        <v>372.8357266958717</v>
       </c>
       <c r="J14" t="n">
         <v>1310</v>
       </c>
       <c r="K14" t="n">
-        <v>2.300000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -986,37 +986,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B15" t="n">
-        <v>100.3</v>
+        <v>100.8</v>
       </c>
       <c r="C15" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>11345.40768887309</v>
+        <v>11301.01250745517</v>
       </c>
       <c r="F15" t="n">
-        <v>1298.038887068986</v>
+        <v>1317.513284557459</v>
       </c>
       <c r="G15" t="n">
         <v>1800</v>
       </c>
       <c r="H15" t="n">
-        <v>11788.23805922321</v>
+        <v>11707.78616617838</v>
       </c>
       <c r="I15" t="n">
-        <v>398.0887422856342</v>
+        <v>395.2339393648352</v>
       </c>
       <c r="J15" t="n">
         <v>1310</v>
       </c>
       <c r="K15" t="n">
-        <v>2.800000000000001</v>
+        <v>1.199999999999999</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -1024,37 +1024,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B16" t="n">
-        <v>100.3</v>
+        <v>101.8</v>
       </c>
       <c r="C16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="D16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>11363.1209036871</v>
+        <v>11303.99874264818</v>
       </c>
       <c r="F16" t="n">
-        <v>1262.040881277652</v>
+        <v>1310.74258301537</v>
       </c>
       <c r="G16" t="n">
         <v>1800</v>
       </c>
       <c r="H16" t="n">
-        <v>11797.09466663022</v>
+        <v>11714.80785433491</v>
       </c>
       <c r="I16" t="n">
-        <v>380.0897393899672</v>
+        <v>379.3136411442485</v>
       </c>
       <c r="J16" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5999999999999979</v>
+        <v>3.599999999999998</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -1062,37 +1062,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B17" t="n">
-        <v>101.3</v>
+        <v>102.8</v>
       </c>
       <c r="C17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>11348.85143452487</v>
+        <v>11306.98497784119</v>
       </c>
       <c r="F17" t="n">
-        <v>1291.040271785526</v>
+        <v>1303.971881473281</v>
       </c>
       <c r="G17" t="n">
         <v>1800</v>
       </c>
       <c r="H17" t="n">
-        <v>11796.09686340291</v>
+        <v>11721.82954249145</v>
       </c>
       <c r="I17" t="n">
-        <v>382.1175433054314</v>
+        <v>363.3933429236614</v>
       </c>
       <c r="J17" t="n">
         <v>1310</v>
       </c>
       <c r="K17" t="n">
-        <v>2.800000000000001</v>
+        <v>0.2999999999999972</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -1100,37 +1100,37 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B18" t="n">
-        <v>102.3</v>
+        <v>104.8</v>
       </c>
       <c r="C18" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>11334.22876068041</v>
+        <v>11287.58251999257</v>
       </c>
       <c r="F18" t="n">
-        <v>1320.75746898914</v>
+        <v>1347.963142303501</v>
       </c>
       <c r="G18" t="n">
         <v>1800</v>
       </c>
       <c r="H18" t="n">
-        <v>11785.88924808636</v>
+        <v>11710.49799056987</v>
       </c>
       <c r="I18" t="n">
-        <v>402.862156812302</v>
+        <v>389.0854103968843</v>
       </c>
       <c r="J18" t="n">
         <v>1310</v>
       </c>
       <c r="K18" t="n">
-        <v>2.099999999999998</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -1138,37 +1138,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>296.2</v>
+        <v>293.8</v>
       </c>
       <c r="B19" t="n">
-        <v>103.3</v>
+        <v>105.8</v>
       </c>
       <c r="C19" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>11337.49590399107</v>
+        <v>11290.32662800776</v>
       </c>
       <c r="F19" t="n">
-        <v>1314.11775705355</v>
+        <v>1341.741416562122</v>
       </c>
       <c r="G19" t="n">
         <v>1800</v>
       </c>
       <c r="H19" t="n">
-        <v>11793.57144992494</v>
+        <v>11717.27755154859</v>
       </c>
       <c r="I19" t="n">
-        <v>387.2498611799684</v>
+        <v>373.7140879770075</v>
       </c>
       <c r="J19" t="n">
         <v>1310</v>
       </c>
       <c r="K19" t="n">
-        <v>3.300000000000001</v>
+        <v>2.799999999999997</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -1176,37 +1176,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>296.2</v>
+        <v>295.4</v>
       </c>
       <c r="B20" t="n">
-        <v>103.3</v>
+        <v>95.8</v>
       </c>
       <c r="C20" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="D20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>11355.73892582842</v>
+        <v>11353.39107770818</v>
       </c>
       <c r="F20" t="n">
-        <v>1277.043041218607</v>
+        <v>1255.760118915784</v>
       </c>
       <c r="G20" t="n">
         <v>1800</v>
       </c>
       <c r="H20" t="n">
-        <v>11802.69296084361</v>
+        <v>11764.3109355084</v>
       </c>
       <c r="I20" t="n">
-        <v>368.7125032624967</v>
+        <v>390.3649083527412</v>
       </c>
       <c r="J20" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6000000000000014</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -1214,37 +1214,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>297.8</v>
+        <v>295.4</v>
       </c>
       <c r="B21" t="n">
-        <v>99.3</v>
+        <v>96.8</v>
       </c>
       <c r="C21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
       </c>
       <c r="E21" t="n">
-        <v>11379.75998576316</v>
+        <v>11357.07991985545</v>
       </c>
       <c r="F21" t="n">
-        <v>1279.721095121366</v>
+        <v>1247.991435397159</v>
       </c>
       <c r="G21" t="n">
         <v>1800</v>
       </c>
       <c r="H21" t="n">
-        <v>11842.88191962067</v>
+        <v>11772.2891289897</v>
       </c>
       <c r="I21" t="n">
-        <v>401.332186732787</v>
+        <v>373.562871905484</v>
       </c>
       <c r="J21" t="n">
         <v>1310</v>
       </c>
       <c r="K21" t="n">
-        <v>1.600000000000001</v>
+        <v>2.399999999999999</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -1252,37 +1252,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>297.8</v>
+        <v>295.4</v>
       </c>
       <c r="B22" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="C22" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E22" t="n">
-        <v>11398.28486311746</v>
+        <v>11339.03032944185</v>
       </c>
       <c r="F22" t="n">
-        <v>1244.585538785823</v>
+        <v>1286.003784520847</v>
       </c>
       <c r="G22" t="n">
         <v>1800</v>
       </c>
       <c r="H22" t="n">
-        <v>11852.14435829782</v>
+        <v>11762.81824124415</v>
       </c>
       <c r="I22" t="n">
-        <v>383.7644085650157</v>
+        <v>393.5085151719056</v>
       </c>
       <c r="J22" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K22" t="n">
-        <v>2.399999999999999</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -1290,37 +1290,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>297.8</v>
+        <v>295.4</v>
       </c>
       <c r="B23" t="n">
-        <v>100.3</v>
+        <v>99.8</v>
       </c>
       <c r="C23" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
         <v>10</v>
       </c>
       <c r="E23" t="n">
-        <v>11383.58435621395</v>
+        <v>11342.46181050907</v>
       </c>
       <c r="F23" t="n">
-        <v>1272.467531124602</v>
+        <v>1278.77710217794</v>
       </c>
       <c r="G23" t="n">
         <v>1800</v>
       </c>
       <c r="H23" t="n">
-        <v>11851.37015647486</v>
+        <v>11770.53907364541</v>
       </c>
       <c r="I23" t="n">
-        <v>385.2328129838729</v>
+        <v>377.248479900366</v>
       </c>
       <c r="J23" t="n">
         <v>1310</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8000000000000007</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1328,37 +1328,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>297.8</v>
+        <v>295.4</v>
       </c>
       <c r="B24" t="n">
-        <v>100.3</v>
+        <v>101.8</v>
       </c>
       <c r="C24" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="D24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E24" t="n">
-        <v>11402.29578822438</v>
+        <v>11323.12541469526</v>
       </c>
       <c r="F24" t="n">
-        <v>1236.978142398973</v>
+        <v>1319.499457180218</v>
       </c>
       <c r="G24" t="n">
         <v>1800</v>
       </c>
       <c r="H24" t="n">
-        <v>11860.72587248008</v>
+        <v>11759.78138049966</v>
       </c>
       <c r="I24" t="n">
-        <v>367.4881186210584</v>
+        <v>399.9041290453779</v>
       </c>
       <c r="J24" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>2.699999999999999</v>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -1366,37 +1366,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>297.8</v>
+        <v>295.4</v>
       </c>
       <c r="B25" t="n">
-        <v>101.3</v>
+        <v>102.8</v>
       </c>
       <c r="C25" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D25" t="n">
         <v>10</v>
       </c>
       <c r="E25" t="n">
-        <v>11368.51073999816</v>
+        <v>11326.29953468244</v>
       </c>
       <c r="F25" t="n">
-        <v>1301.057188243554</v>
+        <v>1312.81477601303</v>
       </c>
       <c r="G25" t="n">
         <v>1800</v>
       </c>
       <c r="H25" t="n">
-        <v>11840.96040666247</v>
+        <v>11767.24485182087</v>
       </c>
       <c r="I25" t="n">
-        <v>404.9766603506735</v>
+        <v>384.1860949495564</v>
       </c>
       <c r="J25" t="n">
         <v>1310</v>
       </c>
       <c r="K25" t="n">
-        <v>1.199999999999999</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
@@ -1404,37 +1404,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>297.8</v>
+        <v>295.4</v>
       </c>
       <c r="B26" t="n">
-        <v>101.3</v>
+        <v>105.8</v>
       </c>
       <c r="C26" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="D26" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E26" t="n">
-        <v>11387.40872666473</v>
+        <v>11308.59309237556</v>
       </c>
       <c r="F26" t="n">
-        <v>1265.213967127838</v>
+        <v>1350.104456902427</v>
       </c>
       <c r="G26" t="n">
         <v>1800</v>
       </c>
       <c r="H26" t="n">
-        <v>11850.40939999576</v>
+        <v>11762.40646351609</v>
       </c>
       <c r="I26" t="n">
-        <v>387.0550497928157</v>
+        <v>394.3757170530545</v>
       </c>
       <c r="J26" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K26" t="n">
-        <v>2.099999999999998</v>
+        <v>3.699999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -1442,37 +1442,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>297.8</v>
+        <v>297</v>
       </c>
       <c r="B27" t="n">
-        <v>102.3</v>
+        <v>96.8</v>
       </c>
       <c r="C27" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="D27" t="n">
         <v>10</v>
       </c>
       <c r="E27" t="n">
-        <v>11372.14855579281</v>
+        <v>11377.93801122318</v>
       </c>
       <c r="F27" t="n">
-        <v>1294.157456636876</v>
+        <v>1258.254888743667</v>
       </c>
       <c r="G27" t="n">
         <v>1800</v>
       </c>
       <c r="H27" t="n">
-        <v>11849.26208886052</v>
+        <v>11817.40081497106</v>
       </c>
       <c r="I27" t="n">
-        <v>389.2311189918448</v>
+        <v>395.760573329327</v>
       </c>
       <c r="J27" t="n">
         <v>1310</v>
       </c>
       <c r="K27" t="n">
-        <v>2.100000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -1480,37 +1480,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>297.8</v>
+        <v>297</v>
       </c>
       <c r="B28" t="n">
-        <v>102.3</v>
+        <v>97.8</v>
       </c>
       <c r="C28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D28" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E28" t="n">
-        <v>11391.23309711552</v>
+        <v>11381.84232952094</v>
       </c>
       <c r="F28" t="n">
-        <v>1257.960403131075</v>
+        <v>1250.592232635648</v>
       </c>
       <c r="G28" t="n">
         <v>1800</v>
       </c>
       <c r="H28" t="n">
-        <v>11858.80435952188</v>
+        <v>11825.84503826621</v>
       </c>
       <c r="I28" t="n">
-        <v>371.1325922389442</v>
+        <v>379.1878519794236</v>
       </c>
       <c r="J28" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K28" t="n">
-        <v>1.099999999999998</v>
+        <v>1.5</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -1518,37 +1518,37 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>297.8</v>
+        <v>297</v>
       </c>
       <c r="B29" t="n">
-        <v>103.3</v>
+        <v>99.8</v>
       </c>
       <c r="C29" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>10</v>
       </c>
       <c r="E29" t="n">
-        <v>11356.51527560862</v>
+        <v>11362.46601499205</v>
       </c>
       <c r="F29" t="n">
-        <v>1323.808610926085</v>
+        <v>1288.620391088007</v>
       </c>
       <c r="G29" t="n">
         <v>1800</v>
       </c>
       <c r="H29" t="n">
-        <v>11838.29267507973</v>
+        <v>11815.54853373212</v>
       </c>
       <c r="I29" t="n">
-        <v>410.0364635289036</v>
+        <v>399.3958799480156</v>
       </c>
       <c r="J29" t="n">
         <v>1310</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3999999999999986</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -1556,37 +1556,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>297.8</v>
+        <v>297</v>
       </c>
       <c r="B30" t="n">
-        <v>103.3</v>
+        <v>100.8</v>
       </c>
       <c r="C30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="D30" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>11375.78637158746</v>
+        <v>11366.09793898997</v>
       </c>
       <c r="F30" t="n">
-        <v>1287.257725030198</v>
+        <v>1281.4923388945</v>
       </c>
       <c r="G30" t="n">
         <v>1800</v>
       </c>
       <c r="H30" t="n">
-        <v>11847.92822306915</v>
+        <v>11823.72036272743</v>
       </c>
       <c r="I30" t="n">
-        <v>391.7610205809601</v>
+        <v>383.3577625126252</v>
       </c>
       <c r="J30" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K30" t="n">
-        <v>0.1999999999999993</v>
+        <v>2.100000000000001</v>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -1594,37 +1594,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>299.4</v>
+        <v>297</v>
       </c>
       <c r="B31" t="n">
-        <v>98.3</v>
+        <v>102.8</v>
       </c>
       <c r="C31" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="D31" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E31" t="n">
-        <v>11434.30255082331</v>
+        <v>11345.35965296187</v>
       </c>
       <c r="F31" t="n">
-        <v>1229.237141301968</v>
+        <v>1322.193516919425</v>
       </c>
       <c r="G31" t="n">
         <v>1800</v>
       </c>
       <c r="H31" t="n">
-        <v>11907.20977283093</v>
+        <v>11812.06188669412</v>
       </c>
       <c r="I31" t="n">
-        <v>389.9620284974451</v>
+        <v>406.2388100537827</v>
       </c>
       <c r="J31" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K31" t="n">
-        <v>2.899999999999999</v>
+        <v>1.299999999999997</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
@@ -1632,37 +1632,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>299.4</v>
+        <v>297</v>
       </c>
       <c r="B32" t="n">
-        <v>99.3</v>
+        <v>103.8</v>
       </c>
       <c r="C32" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="D32" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E32" t="n">
-        <v>11438.72068460585</v>
+        <v>11348.71918265994</v>
       </c>
       <c r="F32" t="n">
-        <v>1221.396217001887</v>
+        <v>1315.600068640431</v>
       </c>
       <c r="G32" t="n">
         <v>1800</v>
       </c>
       <c r="H32" t="n">
-        <v>11916.43876339889</v>
+        <v>11819.96132138959</v>
       </c>
       <c r="I32" t="n">
-        <v>373.5832088483854</v>
+        <v>390.7352965329051</v>
       </c>
       <c r="J32" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K32" t="n">
-        <v>1.399999999999999</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -1670,37 +1670,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>299.4</v>
+        <v>298.6</v>
       </c>
       <c r="B33" t="n">
-        <v>100.3</v>
+        <v>97.8</v>
       </c>
       <c r="C33" t="n">
         <v>8.6</v>
       </c>
       <c r="D33" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E33" t="n">
-        <v>11423.44375979335</v>
+        <v>11402.61814787669</v>
       </c>
       <c r="F33" t="n">
-        <v>1248.508390803947</v>
+        <v>1261.546079027034</v>
       </c>
       <c r="G33" t="n">
         <v>1800</v>
       </c>
       <c r="H33" t="n">
-        <v>11905.97269537181</v>
+        <v>11870.7787849426</v>
       </c>
       <c r="I33" t="n">
-        <v>392.157487301468</v>
+        <v>402.8787290584696</v>
       </c>
       <c r="J33" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K33" t="n">
-        <v>2.899999999999999</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -1708,37 +1708,37 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>299.4</v>
+        <v>298.6</v>
       </c>
       <c r="B34" t="n">
-        <v>101.3</v>
+        <v>100.8</v>
       </c>
       <c r="C34" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E34" t="n">
-        <v>11427.66553207444</v>
+        <v>11386.01711424331</v>
       </c>
       <c r="F34" t="n">
-        <v>1241.015952028313</v>
+        <v>1291.994528614877</v>
       </c>
       <c r="G34" t="n">
         <v>1800</v>
       </c>
       <c r="H34" t="n">
-        <v>11915.00532443833</v>
+        <v>11868.53850704744</v>
       </c>
       <c r="I34" t="n">
-        <v>376.1271531768567</v>
+        <v>406.9876893834728</v>
       </c>
       <c r="J34" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -1746,37 +1746,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>299.4</v>
+        <v>298.6</v>
       </c>
       <c r="B35" t="n">
-        <v>102.3</v>
+        <v>101.8</v>
       </c>
       <c r="C35" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D35" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E35" t="n">
-        <v>11411.7995227576</v>
+        <v>11389.84664910683</v>
       </c>
       <c r="F35" t="n">
-        <v>1269.173582403718</v>
+        <v>1284.970664811453</v>
       </c>
       <c r="G35" t="n">
         <v>1800</v>
       </c>
       <c r="H35" t="n">
-        <v>11903.95017190692</v>
+        <v>11877.15496049037</v>
       </c>
       <c r="I35" t="n">
-        <v>395.7468882032832</v>
+        <v>391.1839958257691</v>
       </c>
       <c r="J35" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K35" t="n">
-        <v>2.399999999999999</v>
+        <v>0.8999999999999986</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -1784,37 +1784,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>299.4</v>
+        <v>298.6</v>
       </c>
       <c r="B36" t="n">
-        <v>103.3</v>
+        <v>104.8</v>
       </c>
       <c r="C36" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="D36" t="n">
         <v>10</v>
       </c>
       <c r="E36" t="n">
-        <v>11395.54079043786</v>
+        <v>11371.2351096701</v>
       </c>
       <c r="F36" t="n">
-        <v>1298.028183828018</v>
+        <v>1319.106642896093</v>
       </c>
       <c r="G36" t="n">
         <v>1800</v>
       </c>
       <c r="H36" t="n">
-        <v>11902.6443679223</v>
+        <v>11872.90417679186</v>
       </c>
       <c r="I36" t="n">
-        <v>398.0643169408627</v>
+        <v>398.9804846475698</v>
       </c>
       <c r="J36" t="n">
         <v>1310</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8999999999999986</v>
+        <v>1.899999999999999</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -1822,37 +1822,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>299.4</v>
+        <v>298.6</v>
       </c>
       <c r="B37" t="n">
-        <v>103.3</v>
+        <v>104.8</v>
       </c>
       <c r="C37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>11415.82493353724</v>
+        <v>11401.33525369741</v>
       </c>
       <c r="F37" t="n">
-        <v>1262.029629152532</v>
+        <v>1263.899073401181</v>
       </c>
       <c r="G37" t="n">
         <v>1800</v>
       </c>
       <c r="H37" t="n">
-        <v>11912.78643947199</v>
+        <v>11887.95424880551</v>
       </c>
       <c r="I37" t="n">
-        <v>380.0650396031197</v>
+        <v>371.3766999001139</v>
       </c>
       <c r="J37" t="n">
-        <v>1329.404</v>
+        <v>1338.959</v>
       </c>
       <c r="K37" t="n">
-        <v>2.800000000000001</v>
+        <v>0.4000000000000021</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -1860,37 +1860,37 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>301</v>
+        <v>300.2</v>
       </c>
       <c r="B38" t="n">
-        <v>99.3</v>
+        <v>98.8</v>
       </c>
       <c r="C38" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>11460.28952754711</v>
+        <v>11457.22501068902</v>
       </c>
       <c r="F38" t="n">
-        <v>1233.949583362522</v>
+        <v>1214.408776016161</v>
       </c>
       <c r="G38" t="n">
         <v>1800</v>
       </c>
       <c r="H38" t="n">
-        <v>11961.49367976508</v>
+        <v>11939.29920674157</v>
       </c>
       <c r="I38" t="n">
-        <v>399.8057963572688</v>
+        <v>386.1223768158081</v>
       </c>
       <c r="J38" t="n">
-        <v>1329.404</v>
+        <v>1338.959</v>
       </c>
       <c r="K38" t="n">
-        <v>2.199999999999999</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -1898,37 +1898,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>301</v>
+        <v>300.2</v>
       </c>
       <c r="B39" t="n">
-        <v>100.3</v>
+        <v>99.8</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>11464.92487022131</v>
+        <v>11461.85279419802</v>
       </c>
       <c r="F39" t="n">
-        <v>1226.235077656203</v>
+        <v>1206.457447838186</v>
       </c>
       <c r="G39" t="n">
         <v>1800</v>
       </c>
       <c r="H39" t="n">
-        <v>11971.17639557339</v>
+        <v>11948.80628373288</v>
       </c>
       <c r="I39" t="n">
-        <v>383.6910511040688</v>
+        <v>369.7875830588831</v>
       </c>
       <c r="J39" t="n">
-        <v>1329.404</v>
+        <v>1338.959</v>
       </c>
       <c r="K39" t="n">
-        <v>3.199999999999999</v>
+        <v>0.2000000000000028</v>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -1936,37 +1936,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>301</v>
+        <v>300.2</v>
       </c>
       <c r="B40" t="n">
-        <v>101.3</v>
+        <v>101.8</v>
       </c>
       <c r="C40" t="n">
         <v>8.6</v>
       </c>
       <c r="D40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>11448.69087010014</v>
+        <v>11440.38390287584</v>
       </c>
       <c r="F40" t="n">
-        <v>1253.252990974334</v>
+        <v>1243.344696385571</v>
       </c>
       <c r="G40" t="n">
         <v>1800</v>
       </c>
       <c r="H40" t="n">
-        <v>11959.98976858635</v>
+        <v>11937.09597937533</v>
       </c>
       <c r="I40" t="n">
-        <v>402.3087248753189</v>
+        <v>389.9079004483656</v>
       </c>
       <c r="J40" t="n">
-        <v>1329.404</v>
+        <v>1338.959</v>
       </c>
       <c r="K40" t="n">
-        <v>2</v>
+        <v>0.8999999999999986</v>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -1974,37 +1974,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>301</v>
+        <v>300.2</v>
       </c>
       <c r="B41" t="n">
-        <v>102.3</v>
+        <v>102.8</v>
       </c>
       <c r="C41" t="n">
         <v>8.6</v>
       </c>
       <c r="D41" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>11453.12019754437</v>
+        <v>11444.70987441686</v>
       </c>
       <c r="F41" t="n">
-        <v>1245.881352188296</v>
+        <v>1235.911933088769</v>
       </c>
       <c r="G41" t="n">
         <v>1800</v>
       </c>
       <c r="H41" t="n">
-        <v>11969.46646916469</v>
+        <v>11946.30124439866</v>
       </c>
       <c r="I41" t="n">
-        <v>386.5368465424002</v>
+        <v>374.0916715726128</v>
       </c>
       <c r="J41" t="n">
-        <v>1329.404</v>
+        <v>1338.959</v>
       </c>
       <c r="K41" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2012,37 +2012,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>301</v>
+        <v>300.2</v>
       </c>
       <c r="B42" t="n">
-        <v>103.3</v>
+        <v>105.8</v>
       </c>
       <c r="C42" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="D42" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>11436.26815173331</v>
+        <v>11425.75608282783</v>
       </c>
       <c r="F42" t="n">
-        <v>1273.927866267269</v>
+        <v>1268.477807626384</v>
       </c>
       <c r="G42" t="n">
         <v>1800</v>
       </c>
       <c r="H42" t="n">
-        <v>11957.66179648776</v>
+        <v>11941.98533325658</v>
       </c>
       <c r="I42" t="n">
-        <v>406.1831210744924</v>
+        <v>381.5071493733753</v>
       </c>
       <c r="J42" t="n">
-        <v>1329.404</v>
+        <v>1338.959</v>
       </c>
       <c r="K42" t="n">
-        <v>1.200000000000003</v>
+        <v>2.300000000000001</v>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -2050,685 +2050,1901 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>287.2</v>
+        <v>301.8</v>
       </c>
       <c r="B43" t="n">
-        <v>120.7</v>
+        <v>97.8</v>
       </c>
       <c r="C43" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>11149.90623888933</v>
+        <v>11505.05551263584</v>
       </c>
       <c r="F43" t="n">
-        <v>1515.731187105699</v>
+        <v>1185.42884733367</v>
       </c>
       <c r="G43" t="n">
         <v>1800</v>
       </c>
       <c r="H43" t="n">
-        <v>11506.82585529249</v>
+        <v>12004.95739759171</v>
       </c>
       <c r="I43" t="n">
-        <v>362.7102040240302</v>
+        <v>379.1696452047519</v>
       </c>
       <c r="J43" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>1.800000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>287.2</v>
+        <v>301.8</v>
       </c>
       <c r="B44" t="n">
-        <v>123.7</v>
+        <v>99.8</v>
       </c>
       <c r="C44" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>11139.00052600371</v>
+        <v>11483.82973319323</v>
       </c>
       <c r="F44" t="n">
-        <v>1550.961853100771</v>
+        <v>1219.662525007181</v>
       </c>
       <c r="G44" t="n">
         <v>1800</v>
       </c>
       <c r="H44" t="n">
-        <v>11504.79138390819</v>
+        <v>11993.95456058174</v>
       </c>
       <c r="I44" t="n">
-        <v>369.2825191554318</v>
+        <v>396.9154046343177</v>
       </c>
       <c r="J44" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K44" t="n">
-        <v>1.800000000000001</v>
+        <v>1.400000000000002</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>287.2</v>
+        <v>301.8</v>
       </c>
       <c r="B45" t="n">
-        <v>124.7</v>
+        <v>100.8</v>
       </c>
       <c r="C45" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>11140.12421659387</v>
+        <v>11488.6777265118</v>
       </c>
       <c r="F45" t="n">
-        <v>1547.331795324706</v>
+        <v>1211.843512231702</v>
       </c>
       <c r="G45" t="n">
         <v>1800</v>
       </c>
       <c r="H45" t="n">
-        <v>11508.8721549988</v>
+        <v>12003.91402511663</v>
       </c>
       <c r="I45" t="n">
-        <v>356.0996777581436</v>
+        <v>380.8524327368658</v>
       </c>
       <c r="J45" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K45" t="n">
-        <v>0.3000000000000007</v>
+        <v>2.199999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>288.8</v>
+        <v>301.8</v>
       </c>
       <c r="B46" t="n">
-        <v>120.7</v>
+        <v>103.8</v>
       </c>
       <c r="C46" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="D46" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>11163.36937154016</v>
+        <v>11470.40289952397</v>
       </c>
       <c r="F46" t="n">
-        <v>1520.105624076949</v>
+        <v>1241.317790824486</v>
       </c>
       <c r="G46" t="n">
         <v>1800</v>
       </c>
       <c r="H46" t="n">
-        <v>11552.34406568338</v>
+        <v>12000.97361177776</v>
       </c>
       <c r="I46" t="n">
-        <v>377.4999671173034</v>
+        <v>385.5948339637324</v>
       </c>
       <c r="J46" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K46" t="n">
-        <v>2.5</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>288.8</v>
+        <v>303.4</v>
       </c>
       <c r="B47" t="n">
-        <v>121.7</v>
+        <v>95.8</v>
       </c>
       <c r="C47" t="n">
-        <v>4.2</v>
+        <v>10.4</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>11164.72288746012</v>
+        <v>11548.45497096148</v>
       </c>
       <c r="F47" t="n">
-        <v>1516.129697184463</v>
+        <v>1168.224376873403</v>
       </c>
       <c r="G47" t="n">
         <v>1800</v>
       </c>
       <c r="H47" t="n">
-        <v>11556.92023855566</v>
+        <v>12059.99470349286</v>
       </c>
       <c r="I47" t="n">
-        <v>364.0575476236604</v>
+        <v>392.4336514572499</v>
       </c>
       <c r="J47" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K47" t="n">
-        <v>1.600000000000001</v>
+        <v>2.800000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>288.8</v>
+        <v>303.4</v>
       </c>
       <c r="B48" t="n">
-        <v>123.7</v>
+        <v>96.8</v>
       </c>
       <c r="C48" t="n">
-        <v>3.8</v>
+        <v>10.4</v>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>11151.48421270005</v>
+        <v>11554.17997065837</v>
       </c>
       <c r="F48" t="n">
-        <v>1555.018048790016</v>
+        <v>1159.541959095463</v>
       </c>
       <c r="G48" t="n">
         <v>1800</v>
       </c>
       <c r="H48" t="n">
-        <v>11550.1268777002</v>
+        <v>12071.05936636857</v>
       </c>
       <c r="I48" t="n">
-        <v>384.0129140268991</v>
+        <v>375.6532094056554</v>
       </c>
       <c r="J48" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K48" t="n">
-        <v>0.2000000000000028</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>288.8</v>
+        <v>303.4</v>
       </c>
       <c r="B49" t="n">
-        <v>124.7</v>
+        <v>98.8</v>
       </c>
       <c r="C49" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>11152.70882234193</v>
+        <v>11532.9974717799</v>
       </c>
       <c r="F49" t="n">
-        <v>1551.420781601576</v>
+        <v>1191.666904873839</v>
       </c>
       <c r="G49" t="n">
         <v>1800</v>
       </c>
       <c r="H49" t="n">
-        <v>11554.57414429438</v>
+        <v>12060.55619384775</v>
       </c>
       <c r="I49" t="n">
-        <v>370.9491542373028</v>
+        <v>391.5821066367211</v>
       </c>
       <c r="J49" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K49" t="n">
-        <v>2.699999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>288.8</v>
+        <v>303.4</v>
       </c>
       <c r="B50" t="n">
-        <v>125.7</v>
+        <v>99.8</v>
       </c>
       <c r="C50" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>11153.93343198381</v>
+        <v>11538.39218303273</v>
       </c>
       <c r="F50" t="n">
-        <v>1547.823514413137</v>
+        <v>1183.485395813858</v>
       </c>
       <c r="G50" t="n">
         <v>1800</v>
       </c>
       <c r="H50" t="n">
-        <v>11559.02141088856</v>
+        <v>12071.29056827941</v>
       </c>
       <c r="I50" t="n">
-        <v>357.8853944477062</v>
+        <v>375.3025733030846</v>
       </c>
       <c r="J50" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K50" t="n">
-        <v>0.5</v>
+        <v>0.5999999999999979</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>290.4</v>
+        <v>303.4</v>
       </c>
       <c r="B51" t="n">
-        <v>121.7</v>
+        <v>101.8</v>
       </c>
       <c r="C51" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>11178.16911626807</v>
+        <v>11515.558241934</v>
       </c>
       <c r="F51" t="n">
-        <v>1520.917683891114</v>
+        <v>1218.114885182024</v>
       </c>
       <c r="G51" t="n">
         <v>1800</v>
       </c>
       <c r="H51" t="n">
-        <v>11602.38129785872</v>
+        <v>12059.13595353833</v>
       </c>
       <c r="I51" t="n">
-        <v>380.2455026794823</v>
+        <v>393.7360141239405</v>
       </c>
       <c r="J51" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K51" t="n">
-        <v>3.299999999999997</v>
+        <v>3.599999999999998</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>290.4</v>
+        <v>303.4</v>
       </c>
       <c r="B52" t="n">
-        <v>122.7</v>
+        <v>102.8</v>
       </c>
       <c r="C52" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>11179.63311886682</v>
+        <v>11520.62266474278</v>
       </c>
       <c r="F52" t="n">
-        <v>1516.981099535249</v>
+        <v>1210.434284840001</v>
       </c>
       <c r="G52" t="n">
         <v>1800</v>
       </c>
       <c r="H52" t="n">
-        <v>11607.33102093069</v>
+        <v>12069.54003952594</v>
       </c>
       <c r="I52" t="n">
-        <v>366.9360984286977</v>
+        <v>377.9573895082622</v>
       </c>
       <c r="J52" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K52" t="n">
-        <v>2.100000000000001</v>
+        <v>1.099999999999998</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>290.4</v>
+        <v>303.4</v>
       </c>
       <c r="B53" t="n">
-        <v>124.7</v>
+        <v>104.8</v>
       </c>
       <c r="C53" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="D53" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>11165.17435034392</v>
+        <v>11496.1372814238</v>
       </c>
       <c r="F53" t="n">
-        <v>1555.859556459372</v>
+        <v>1247.568317797957</v>
       </c>
       <c r="G53" t="n">
         <v>1800</v>
       </c>
       <c r="H53" t="n">
-        <v>11599.84369335422</v>
+        <v>12055.73398256461</v>
       </c>
       <c r="I53" t="n">
-        <v>387.0689155629834</v>
+        <v>398.8953739189086</v>
       </c>
       <c r="J53" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K53" t="n">
-        <v>2.800000000000001</v>
+        <v>3.100000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>290.4</v>
+        <v>303.4</v>
       </c>
       <c r="B54" t="n">
-        <v>125.7</v>
+        <v>105.8</v>
       </c>
       <c r="C54" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="D54" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>11166.49892412374</v>
+        <v>11500.87141578854</v>
       </c>
       <c r="F54" t="n">
-        <v>1552.297884899303</v>
+        <v>1240.388626173892</v>
       </c>
       <c r="G54" t="n">
         <v>1800</v>
       </c>
       <c r="H54" t="n">
-        <v>11604.65398760726</v>
+        <v>12065.80778010816</v>
       </c>
       <c r="I54" t="n">
-        <v>374.1344241079953</v>
+        <v>383.6176580211883</v>
       </c>
       <c r="J54" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K54" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B55" t="n">
-        <v>120.7</v>
+        <v>97.8</v>
       </c>
       <c r="C55" t="n">
-        <v>4.6</v>
+        <v>10.4</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>11207.98907279638</v>
+        <v>11583.39606494138</v>
       </c>
       <c r="F55" t="n">
-        <v>1485.208980267428</v>
+        <v>1166.824072712781</v>
       </c>
       <c r="G55" t="n">
         <v>1800</v>
       </c>
       <c r="H55" t="n">
-        <v>11660.13923104939</v>
+        <v>12127.52508705016</v>
       </c>
       <c r="I55" t="n">
-        <v>366.0980678053156</v>
+        <v>389.727294377586</v>
       </c>
       <c r="J55" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K55" t="n">
-        <v>1.200000000000003</v>
+        <v>2.5</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B56" t="n">
-        <v>121.7</v>
+        <v>99.8</v>
       </c>
       <c r="C56" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>11191.47641415861</v>
+        <v>11560.98069780878</v>
       </c>
       <c r="F56" t="n">
-        <v>1526.079244576732</v>
+        <v>1198.836534603594</v>
       </c>
       <c r="G56" t="n">
         <v>1800</v>
       </c>
       <c r="H56" t="n">
-        <v>11647.37263834577</v>
+        <v>12116.23710278277</v>
       </c>
       <c r="I56" t="n">
-        <v>397.6964935689518</v>
+        <v>405.848206609193</v>
       </c>
       <c r="J56" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K56" t="n">
-        <v>1.5</v>
+        <v>0.6000000000000014</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B57" t="n">
-        <v>122.7</v>
+        <v>100.8</v>
       </c>
       <c r="C57" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>11193.04976185096</v>
+        <v>11566.60174688502</v>
       </c>
       <c r="F57" t="n">
-        <v>1522.185072387552</v>
+        <v>1190.808844569562</v>
       </c>
       <c r="G57" t="n">
         <v>1800</v>
       </c>
       <c r="H57" t="n">
-        <v>11652.69205197228</v>
+        <v>12127.42184329162</v>
       </c>
       <c r="I57" t="n">
-        <v>384.5304828341036</v>
+        <v>389.8747417455578</v>
       </c>
       <c r="J57" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K57" t="n">
-        <v>3.599999999999998</v>
+        <v>2.600000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B58" t="n">
-        <v>123.7</v>
+        <v>102.8</v>
       </c>
       <c r="C58" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>11194.6231095433</v>
+        <v>11542.46565044337</v>
       </c>
       <c r="F58" t="n">
-        <v>1518.290900198371</v>
+        <v>1225.278762593243</v>
       </c>
       <c r="G58" t="n">
         <v>1800</v>
       </c>
       <c r="H58" t="n">
-        <v>11658.01146559879</v>
+        <v>12114.41312971517</v>
       </c>
       <c r="I58" t="n">
-        <v>371.3644720992552</v>
+        <v>408.4531101100324</v>
       </c>
       <c r="J58" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K58" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="B59" t="n">
-        <v>125.7</v>
+        <v>103.8</v>
       </c>
       <c r="C59" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D59" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>11178.93458541105</v>
+        <v>11547.7425536578</v>
       </c>
       <c r="F59" t="n">
-        <v>1557.121360027628</v>
+        <v>1217.742563785785</v>
       </c>
       <c r="G59" t="n">
         <v>1800</v>
       </c>
       <c r="H59" t="n">
-        <v>11649.81507333485</v>
+        <v>12125.25372436221</v>
       </c>
       <c r="I59" t="n">
-        <v>391.6512548371763</v>
+        <v>392.9711364729703</v>
       </c>
       <c r="J59" t="n">
-        <v>1310</v>
+        <v>1338.959</v>
       </c>
       <c r="K59" t="n">
-        <v>3.400000000000002</v>
+        <v>2.699999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>292</v>
+        <v>286.4</v>
       </c>
       <c r="B60" t="n">
-        <v>125.7</v>
+        <v>122.2</v>
       </c>
       <c r="C60" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="E60" t="n">
-        <v>11197.769804928</v>
+        <v>11138.0085041048</v>
       </c>
       <c r="F60" t="n">
-        <v>1510.50255582001</v>
+        <v>1531.08732924482</v>
       </c>
       <c r="G60" t="n">
         <v>1800</v>
       </c>
       <c r="H60" t="n">
-        <v>11659.23268309332</v>
+        <v>11483.02976436679</v>
       </c>
       <c r="I60" t="n">
-        <v>368.3418527333672</v>
+        <v>358.8056523568694</v>
       </c>
       <c r="J60" t="n">
-        <v>1329.404</v>
+        <v>1310</v>
       </c>
       <c r="K60" t="n">
-        <v>0.4000000000000021</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="L60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="B61" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>11122.10703325541</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1585.115892290916</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H61" t="n">
+        <v>11481.24536635954</v>
+      </c>
+      <c r="I61" t="n">
+        <v>364.8685166759628</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1.300000000000001</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>288</v>
+      </c>
+      <c r="B62" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="n">
+        <v>11168.01872018155</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1482.891550959999</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H62" t="n">
+        <v>11533.27680753273</v>
+      </c>
+      <c r="I62" t="n">
+        <v>358.7427486991276</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>288</v>
+      </c>
+      <c r="B63" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="n">
+        <v>11151.04750685047</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1535.123574834929</v>
+      </c>
+      <c r="G63" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H63" t="n">
+        <v>11528.66627397666</v>
+      </c>
+      <c r="I63" t="n">
+        <v>372.932511922251</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>288</v>
+      </c>
+      <c r="B64" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="n">
+        <v>11152.28357482797</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1531.319348769748</v>
+      </c>
+      <c r="G64" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H64" t="n">
+        <v>11532.99251189791</v>
+      </c>
+      <c r="I64" t="n">
+        <v>359.617720694119</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>288</v>
+      </c>
+      <c r="B65" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="n">
+        <v>11133.64366972728</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1588.687077832672</v>
+      </c>
+      <c r="G65" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H65" t="n">
+        <v>11526.71328657221</v>
+      </c>
+      <c r="I65" t="n">
+        <v>378.9431891052368</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1.900000000000002</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>288</v>
+      </c>
+      <c r="B66" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="n">
+        <v>11134.69432750815</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1585.453485677268</v>
+      </c>
+      <c r="G66" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H66" t="n">
+        <v>11530.85411429684</v>
+      </c>
+      <c r="I66" t="n">
+        <v>366.1990317868815</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1.899999999999999</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="B67" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="n">
+        <v>11182.39172750461</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1487.784521770491</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H67" t="n">
+        <v>11578.89548294941</v>
+      </c>
+      <c r="I67" t="n">
+        <v>374.2726125759068</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="B68" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="n">
+        <v>11183.93480472546</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1483.451057487669</v>
+      </c>
+      <c r="G68" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H68" t="n">
+        <v>11583.79307586776</v>
+      </c>
+      <c r="I68" t="n">
+        <v>360.5185737652121</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="B69" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="n">
+        <v>11165.31053357293</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1535.75408726642</v>
+      </c>
+      <c r="G69" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H69" t="n">
+        <v>11578.58686750524</v>
+      </c>
+      <c r="I69" t="n">
+        <v>375.1393054324712</v>
+      </c>
+      <c r="J69" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K69" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="B70" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="n">
+        <v>11166.65233985193</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1531.985857455271</v>
+      </c>
+      <c r="G70" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H70" t="n">
+        <v>11583.28318948174</v>
+      </c>
+      <c r="I70" t="n">
+        <v>361.950501093449</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1.299999999999997</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>289.6</v>
+      </c>
+      <c r="B71" t="n">
+        <v>128.2</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="n">
+        <v>11146.21663022274</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1589.375997479073</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H71" t="n">
+        <v>11576.26554264257</v>
+      </c>
+      <c r="I71" t="n">
+        <v>381.6583430057594</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3.100000000000001</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="B72" t="n">
+        <v>118.2</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="n">
+        <v>11196.62251124504</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1493.076902803102</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H72" t="n">
+        <v>11624.06275308207</v>
+      </c>
+      <c r="I72" t="n">
+        <v>391.0701697663662</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="B73" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="n">
+        <v>11198.28598426741</v>
+      </c>
+      <c r="F73" t="n">
+        <v>1488.78821331751</v>
+      </c>
+      <c r="G73" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H73" t="n">
+        <v>11629.34247180527</v>
+      </c>
+      <c r="I73" t="n">
+        <v>377.4582422686196</v>
+      </c>
+      <c r="J73" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3.599999999999998</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="B74" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="n">
+        <v>11199.94945728979</v>
+      </c>
+      <c r="F74" t="n">
+        <v>1484.499523831919</v>
+      </c>
+      <c r="G74" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H74" t="n">
+        <v>11634.62219052847</v>
+      </c>
+      <c r="I74" t="n">
+        <v>363.8463147708731</v>
+      </c>
+      <c r="J74" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1.199999999999999</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="B75" t="n">
+        <v>123.2</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11178.20858813645</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1540.550830760996</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H75" t="n">
+        <v>11623.73005847759</v>
+      </c>
+      <c r="I75" t="n">
+        <v>391.9279076634848</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="B76" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="n">
+        <v>11179.65508641678</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1536.821535556134</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H76" t="n">
+        <v>11628.79280245874</v>
+      </c>
+      <c r="I76" t="n">
+        <v>378.8753744464673</v>
+      </c>
+      <c r="J76" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K76" t="n">
+        <v>3.600000000000001</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="B77" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="n">
+        <v>11181.10158469711</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1533.092240351271</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H77" t="n">
+        <v>11633.85554643989</v>
+      </c>
+      <c r="I77" t="n">
+        <v>365.82284122945</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="B78" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="C78" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="n">
+        <v>11212.48254636342</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1494.523996720993</v>
+      </c>
+      <c r="G78" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H78" t="n">
+        <v>11674.40112541432</v>
+      </c>
+      <c r="I78" t="n">
+        <v>395.6631200275008</v>
+      </c>
+      <c r="J78" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K78" t="n">
+        <v>3</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="B79" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="n">
+        <v>11214.2651180611</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1490.283426223686</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H79" t="n">
+        <v>11680.05885297652</v>
+      </c>
+      <c r="I79" t="n">
+        <v>382.2039180143088</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="B80" t="n">
+        <v>124.2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="n">
+        <v>11192.5177433494</v>
+      </c>
+      <c r="F80" t="n">
+        <v>1542.018386290833</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H80" t="n">
+        <v>11673.81210172292</v>
+      </c>
+      <c r="I80" t="n">
+        <v>397.0643520179156</v>
+      </c>
+      <c r="J80" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>292.8</v>
+      </c>
+      <c r="B81" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="n">
+        <v>11194.06780569521</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1538.330933684479</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H81" t="n">
+        <v>11679.23731993325</v>
+      </c>
+      <c r="I81" t="n">
+        <v>384.1582678956765</v>
+      </c>
+      <c r="J81" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3.400000000000002</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="B82" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="C82" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="n">
+        <v>11228.41370133859</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1496.464790267049</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H82" t="n">
+        <v>11724.96522598769</v>
+      </c>
+      <c r="I82" t="n">
+        <v>401.8230299780234</v>
+      </c>
+      <c r="J82" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="B83" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="n">
+        <v>11230.31398171578</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1492.27564542734</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H83" t="n">
+        <v>11730.99655066312</v>
+      </c>
+      <c r="I83" t="n">
+        <v>388.5270485302533</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K83" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="B84" t="n">
+        <v>125.2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="n">
+        <v>11206.88269845613</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1543.929622668267</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H84" t="n">
+        <v>11724.08944459646</v>
+      </c>
+      <c r="I84" t="n">
+        <v>403.7536793389329</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K84" t="n">
+        <v>3.400000000000002</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>294.4</v>
+      </c>
+      <c r="B85" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="n">
+        <v>11208.53511617543</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1540.286888025042</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H85" t="n">
+        <v>11729.872906614</v>
+      </c>
+      <c r="I85" t="n">
+        <v>391.0041080876465</v>
+      </c>
+      <c r="J85" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K85" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>296</v>
+      </c>
+      <c r="B86" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="n">
+        <v>11244.40068175785</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1498.904343307288</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H86" t="n">
+        <v>11775.70651166621</v>
+      </c>
+      <c r="I86" t="n">
+        <v>409.5659591926978</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>296</v>
+      </c>
+      <c r="B87" t="n">
+        <v>121.2</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E87" t="n">
+        <v>11276.27903155235</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1433.544040260413</v>
+      </c>
+      <c r="G87" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H87" t="n">
+        <v>11791.64568656346</v>
+      </c>
+      <c r="I87" t="n">
+        <v>376.8858076692602</v>
+      </c>
+      <c r="J87" t="n">
+        <v>1338.959</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>296</v>
+      </c>
+      <c r="B88" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="n">
+        <v>11246.41718903308</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1494.769890694312</v>
+      </c>
+      <c r="G88" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H88" t="n">
+        <v>11782.10673040933</v>
+      </c>
+      <c r="I88" t="n">
+        <v>396.4435661167304</v>
+      </c>
+      <c r="J88" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K88" t="n">
+        <v>3.300000000000001</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>296</v>
+      </c>
+      <c r="B89" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="n">
+        <v>11221.28975489913</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1546.288765428181</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H89" t="n">
+        <v>11774.51414214694</v>
+      </c>
+      <c r="I89" t="n">
+        <v>412.0106789986319</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2.900000000000002</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>296</v>
+      </c>
+      <c r="B90" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D90" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E90" t="n">
+        <v>11254.483218134</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1478.232080242408</v>
+      </c>
+      <c r="G90" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H90" t="n">
+        <v>11791.11087376438</v>
+      </c>
+      <c r="I90" t="n">
+        <v>377.9823364057454</v>
+      </c>
+      <c r="J90" t="n">
+        <v>1338.959</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1.399999999999999</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>296</v>
+      </c>
+      <c r="B91" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4</v>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="n">
+        <v>11223.04323948628</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1542.693589242984</v>
+      </c>
+      <c r="G91" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H91" t="n">
+        <v>11780.65133820199</v>
+      </c>
+      <c r="I91" t="n">
+        <v>399.4275623504434</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1310</v>
+      </c>
+      <c r="K91" t="n">
+        <v>3.399999999999999</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>296</v>
+      </c>
+      <c r="B92" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D92" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E92" t="n">
+        <v>11256.49972540922</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1474.097627629431</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H92" t="n">
+        <v>11797.37958116346</v>
+      </c>
+      <c r="I92" t="n">
+        <v>365.1295815436674</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1338.959</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="L92" t="n">
         <v>0</v>
       </c>
     </row>
